--- a/outputs/evaluation/decision/v2/CF_M08/run_2/CF_M08_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M08/run_2/CF_M08_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_07</t>
+          <t>R_28, C_07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12g. Expansion or Growth Requirements</t>
+          <t>The system must be scalable to handle an increase in the number of users and volume of data.; 12g. Expansion or Growth Requirements</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -506,216 +506,116 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6187</v>
+        <v>0.6722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects... When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_02, C_06</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11a. Ease of Use Requirements; 14c. Adaptability Requirements</t>
+          <t>14a. Maintenance Requirements</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7467</v>
+        <v>0.6006</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
+          <t>Docker is a containerization platform used to manage the execution of the application services.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>C_05, C_06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14a. Maintenance Requirements</t>
+          <t>14a. Maintenance Requirements; 14c. Adaptability Requirements</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Component-Based</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>It is designed to simplify access and database management</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.7407</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is used generally to manage shared resources, such as configurations, logs, or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C_04, Performance</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>12e. Robustness or Fault Tolerance Requirements; Performance</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Singleton Pattern</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD10</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>It is designed to simplify access and database management</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6389</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Docker is used to create an application and package it together with its dependencies and libraries in a container, allowing to develop locally, raise a database, and build an image that can be deployed in different environments.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C_05, C_06</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>14a. Maintenance Requirements; 14c. Adaptability Requirements</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CF_M08_AD07</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.6415</v>
+        <v>0.6791</v>
       </c>
     </row>
   </sheetData>
